--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), il reste environ 180 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), il reste environ 121 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), il reste environ 121 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), il reste environ 180 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), il reste environ 180 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 195 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>L’ensemble se situe au rez-de-chaussée d’un immeuble en pierre de taille édifié en 1908 dans une rue calme et typiquement résidentielle du 15? arrondissement. Le bâtiment offre une accessibilité aisée depuis les transports en commun et bénéficie d’un environnement dynamique grâce à la densité des commerces, services bancaires, restaurants et équipements publics situés à quelques minutes à pied. Les parties communes présentent le charme caractéristique des immeubles de cette époque et participent à l’attractivité générale du site.</t>
+          <t>Prix de vente : 188600 € Autre : Local vendu vide et immédiatement disponible L’ensemble se situe au rez-de-chaussée d’un immeuble en pierre de taille édifié en 1908 dans une rue calme et typiquement résidentielle du 15? arrondissement. Le bâtiment offre une accessibilité aisée depuis les transports en commun et bénéficie d’un environnement dynamique grâce à la densité des commerces, services bancaires, restaurants et équipements publics situés à quelques minutes à pied. Les parties communes présentent le charme caractéristique des immeubles de cette époque et participent à l’attractivité générale du site.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 195 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 208 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-b6a558c6.xlsx
+++ b/docs/dossiers/dossier-paris-b6a558c6.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
